--- a/results/Int All Data 0.4/Rando_7_permute.xlsx
+++ b/results/Int All Data 0.4/Rando_7_permute.xlsx
@@ -440,57 +440,57 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8145912748835239</v>
+        <v>0.9118619229140195</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8132892842016095</v>
+        <v>0.8995442609063956</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8146226175349429</v>
+        <v>0.8432579415501906</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8149402795425666</v>
+        <v>0.8425912748835239</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7999559508682762</v>
+        <v>0.8375756035578145</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7989089368911478</v>
+        <v>0.8215756035578146</v>
       </c>
     </row>
     <row r="8">
@@ -500,327 +500,327 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.800591274883524</v>
+        <v>0.8242736128759001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7912892842016095</v>
+        <v>0.8196069462092334</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7946226175349429</v>
+        <v>0.8065599322321051</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7936069462092333</v>
+        <v>0.8065599322321051</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7936069462092333</v>
+        <v>0.7898932655654384</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7905599322321051</v>
+        <v>0.7898932655654384</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7908775942397289</v>
+        <v>0.7985599322321051</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7933206268530284</v>
+        <v>0.8018932655654384</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7933206268530284</v>
+        <v>0.7835442609063956</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7883049555273189</v>
+        <v>0.7825599322321051</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7869716221939855</v>
+        <v>0.7869089368911478</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.773132570944515</v>
+        <v>0.7879246082168572</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.773132570944515</v>
+        <v>0.7912579415501906</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7737992376111817</v>
+        <v>0.7956069462092333</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7734815756035578</v>
+        <v>0.7969089368911478</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7678305802626006</v>
+        <v>0.7969089368911478</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7658932655654384</v>
+        <v>0.7915756035578145</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7679246082168573</v>
+        <v>0.7942422702244811</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7679246082168573</v>
+        <v>0.7942422702244811</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7732579415501906</v>
+        <v>0.7942422702244811</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.776591274883524</v>
+        <v>0.7936382888606524</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.776591274883524</v>
+        <v>0.7919559508682762</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7756069462092334</v>
+        <v>0.7979246082168572</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7606226175349429</v>
+        <v>0.794591274883524</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.760591274883524</v>
+        <v>0.8029089368911478</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.760591274883524</v>
+        <v>0.8015756035578145</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.758591274883524</v>
+        <v>0.8015756035578145</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.7579246082168573</v>
+        <v>0.8015756035578145</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7676069462092334</v>
+        <v>0.8062422702244811</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.7799288437102923</v>
+        <v>0.8055756035578145</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.77970944515036</v>
+        <v>0.8055756035578145</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7730072003388395</v>
+        <v>0.8049089368911477</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.7730072003388395</v>
+        <v>0.8025285895806862</v>
       </c>
     </row>
     <row r="41">
@@ -830,827 +830,827 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7736738670055061</v>
+        <v>0.8021795849216433</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7736738670055061</v>
+        <v>0.8021795849216433</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7652308343922067</v>
+        <v>0.8291952562473528</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7618034731046166</v>
+        <v>0.8195129182549767</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7590741211351122</v>
+        <v>0.82484625158831</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.75856416772554</v>
+        <v>0.8101795849216433</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7534858110969928</v>
+        <v>0.81484625158831</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7522465057179162</v>
+        <v>0.8141795849216433</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.7506268530283777</v>
+        <v>0.8241795849216433</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.7503091910207539</v>
+        <v>0.8341795849216433</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.7509758576874206</v>
+        <v>0.8458619229140195</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.75199152901313</v>
+        <v>0.8378619229140195</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7523718763235917</v>
+        <v>0.8386226175349428</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7533875476493012</v>
+        <v>0.8519559508682761</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7667835662854723</v>
+        <v>0.8468775942397289</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7534502329521389</v>
+        <v>0.8495442609063957</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7534502329521389</v>
+        <v>0.8368462515883099</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7597992376111817</v>
+        <v>0.8464032189750106</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7591012282930962</v>
+        <v>0.8514815756035579</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7587835662854723</v>
+        <v>0.8471952562473528</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7574502329521389</v>
+        <v>0.8842109275730623</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.7515442609063956</v>
+        <v>0.8715713680643795</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.7529716221939856</v>
+        <v>0.8846539601863617</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7550969927996611</v>
+        <v>0.8876382888606522</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7496611605252012</v>
+        <v>0.8801711139347734</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7509318085556967</v>
+        <v>0.8795044472681067</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7509318085556967</v>
+        <v>0.8797907666243117</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7626810673443456</v>
+        <v>0.8857907666243117</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7602024565861922</v>
+        <v>0.8907750952986022</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7602024565861922</v>
+        <v>0.8855628970775096</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7703634053367217</v>
+        <v>0.8865158831003812</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.773728081321474</v>
+        <v>0.8865158831003812</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.782292249047014</v>
+        <v>0.8963235916984329</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7760813214739517</v>
+        <v>0.9140601440067768</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.7767479881406184</v>
+        <v>0.9100559085133417</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7804930114358323</v>
+        <v>0.9081812791190174</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.768570097416349</v>
+        <v>0.9096128759000424</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7727268106734435</v>
+        <v>0.9027581533248623</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7780914866581957</v>
+        <v>0.9200186361711139</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.7777738246505719</v>
+        <v>0.9183676408301567</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7839347734011013</v>
+        <v>0.9240499788225329</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7826327827191868</v>
+        <v>0.9316653960186362</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7836171113934773</v>
+        <v>0.9450385429902584</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7832681067344346</v>
+        <v>0.9480228716645489</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7711342651418891</v>
+        <v>0.9513562049978823</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7734832698009317</v>
+        <v>0.9478305802626006</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7961541719610334</v>
+        <v>0.9421482422702245</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7894205844980939</v>
+        <v>0.9372892842016095</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7967581533248624</v>
+        <v>0.9360813214739517</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.788561626429479</v>
+        <v>0.9391596781024989</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7812240576027107</v>
+        <v>0.9425328250741212</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7759263024142313</v>
+        <v>0.9398034731046166</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7667767894959763</v>
+        <v>0.9398034731046166</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7687141041931385</v>
+        <v>0.9202465057179161</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7928293096145701</v>
+        <v>0.9202465057179161</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.7961939855993223</v>
+        <v>0.9144074544684456</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.7859119017365523</v>
+        <v>0.9104074544684456</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.7823235916984328</v>
+        <v>0.8892037272342228</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.7771825497670479</v>
+        <v>0.8888860652265989</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.7781355357899196</v>
+        <v>0.8752037272342228</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.7752765777213045</v>
+        <v>0.8809174078780178</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.7756569250317662</v>
+        <v>0.8809174078780178</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.772864887759424</v>
+        <v>0.8715840745446845</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.7670529436679373</v>
+        <v>0.8668775942397289</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.7690885218127912</v>
+        <v>0.8409758576874206</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.7667081745023295</v>
+        <v>0.799168149089369</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.7697509529860229</v>
+        <v>0.7985328250741212</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.7613748411689962</v>
+        <v>0.7683718763235917</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.7613748411689962</v>
+        <v>0.7720542143159679</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.7344531977975435</v>
+        <v>0.8083676408301567</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.7418805590851334</v>
+        <v>0.7927479881406183</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.7447666243117324</v>
+        <v>0.8181753494282085</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7447666243117324</v>
+        <v>0.7944303261329945</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.6955044472681068</v>
+        <v>0.7823049555273189</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.6869047013977129</v>
+        <v>0.7703049555273189</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.6679246082168573</v>
+        <v>0.7709716221939856</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.6624303261329945</v>
+        <v>0.7903989834815757</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.6574459974587039</v>
+        <v>0.7824616687844135</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.6287793307920373</v>
+        <v>0.7985243540872511</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.6092452350698856</v>
+        <v>0.7870656501482423</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5892452350698856</v>
+        <v>0.7758305802626007</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5926683608640406</v>
+        <v>0.7785201185938162</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.6067268106734435</v>
+        <v>0.7394061838204151</v>
       </c>
     </row>
     <row r="124">
@@ -1660,327 +1660,327 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.6298280389665396</v>
+        <v>0.728010165184244</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.625993223210504</v>
+        <v>0.7382922490470141</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.6244362558238035</v>
+        <v>0.7334688691232529</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.6203693350275307</v>
+        <v>0.7054561626429479</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.6233850063532402</v>
+        <v>0.7178280389665397</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.6283693350275307</v>
+        <v>0.7168123676408302</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.6135959339263024</v>
+        <v>0.7767056332062685</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.6155959339263024</v>
+        <v>0.7600304955527319</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.6177526471833968</v>
+        <v>0.7219508682761542</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.6174976704786108</v>
+        <v>0.7079237611181703</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.5385785684032189</v>
+        <v>0.6949394324438798</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5163862770012707</v>
+        <v>0.663127488352393</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5295671325709445</v>
+        <v>0.6321846675137653</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.533723845828039</v>
+        <v>0.6321846675137653</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.533723845828039</v>
+        <v>0.6562761541719611</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.5323905124947056</v>
+        <v>0.6540567556120287</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.5276255823803473</v>
+        <v>0.6444870817450233</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.5292409995764507</v>
+        <v>0.6456408301567133</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.5610673443456162</v>
+        <v>0.6258788648877593</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.5675916984328675</v>
+        <v>0.6258788648877593</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.565430749682338</v>
+        <v>0.500279542566709</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.5569563744176196</v>
+        <v>0.5515281660313427</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.5569563744176196</v>
+        <v>0.5392121982210928</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.5564337145277425</v>
+        <v>0.6475612028801355</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.5564337145277425</v>
+        <v>0.6523134265141889</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.5564337145277425</v>
+        <v>0.6561253706056756</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.557990681914443</v>
+        <v>0.5480381194409149</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5276781024989412</v>
+        <v>0.5439169843286743</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5157365523083439</v>
+        <v>0.5190978398983481</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.5157365523083439</v>
+        <v>0.5210707327403643</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4778432867429055</v>
+        <v>0.5066378653113088</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4906293943244388</v>
+        <v>0.5066378653113088</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5079102075391783</v>
+        <v>0.5063202033036849</v>
       </c>
     </row>
   </sheetData>
